--- a/doc/명지대813자리배치.xlsx
+++ b/doc/명지대813자리배치.xlsx
@@ -9,10 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12285"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12285" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="자리배치0519" sheetId="3" r:id="rId2"/>
+    <sheet name="팀배치" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,85 +26,174 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>이승민</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>서준원</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김호중</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>진서현</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이예서</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이해성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>정현서</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>정윤석</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>배준성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>박수빈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이성복</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>손기현</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>정해훈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>안성준</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김성민</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>윤종혁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>장민준</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이진환</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="43">
   <si>
     <t>명지대 813 배치</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>류한호</t>
+    <t>ㄷ.</t>
+  </si>
+  <si>
+    <t>ㄴ.</t>
+  </si>
+  <si>
+    <t>ㄱ.</t>
+  </si>
+  <si>
+    <t>손기현(26,전공),L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이성복(22,전공),?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안성준(23,정통),B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정해훈(22,정통),?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진서연(21,컴공),F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이예서(21,컴공),?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정현서(24,전공),L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배준성(24,전공),?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이해성(23,전공),?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박수빈(23,컴보),L,B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서준원(23,컴공),B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>윤종혁(23,컴공),F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정윤석(24,컴보),?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이진환(26,컴공),L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장민준(21,컴공),?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김호중(24,전공),?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>류한호(21,전공),?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김성민(23,컴보),B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>명지대 813 배치 (칠판)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>손기현(26,전공),L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정현서(24,전공),L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박수빈(23,컴보),L,B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이진환(26,컴공),L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안성준(23,정통),B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배준성(24,전공),?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서준원(23,컴공),B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장민준(21,컴공),?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정해훈(22,정통),?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이해성(23,전공),?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>윤종혁(23,컴공),F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김호중(24,전공),?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이성복(22,전공),?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이예서(21,컴공),?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정윤석(24,컴보),?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>류한호(21,전공),?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진서연(21,컴공),F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김성민(23,컴보),B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅁ.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄹ.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -110,7 +201,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,13 +217,65 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF99FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -164,14 +307,38 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -180,6 +347,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF99FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -455,110 +627,115 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I9"/>
-  <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="20.625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.625" customWidth="1"/>
-    <col min="4" max="4" width="1.875" customWidth="1"/>
-    <col min="7" max="7" width="1.75" customWidth="1"/>
+    <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="29.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="29.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="20.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+    </row>
+    <row r="4" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="4" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="E4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="1"/>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="C5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="1"/>
-      <c r="C6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I6" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="E9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="H9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="1"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -567,4 +744,222 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:I9"/>
+  <sheetFormatPr defaultColWidth="20.625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="29.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="29.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="20.625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+    </row>
+    <row r="4" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="E5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="E6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="H8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="E9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:I2"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:T8"/>
+  <sheetFormatPr defaultRowHeight="38.25" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>